--- a/excel/Revolut Brokerage Rima.xlsx
+++ b/excel/Revolut Brokerage Rima.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Revolut\Brokerage Account Rima\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Revolut\Brokerage Account Rima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8654966-5288-4CA6-AD04-03807BDD7062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EE1FC9-214D-466E-AEDD-AC0AB94F2565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="81" r:id="rId1"/>
@@ -22,13 +22,14 @@
     <sheet name="XDWT" sheetId="86" state="hidden" r:id="rId7"/>
     <sheet name="XAIX" sheetId="87" state="hidden" r:id="rId8"/>
     <sheet name="WEBN" sheetId="90" r:id="rId9"/>
-    <sheet name="2026.07" sheetId="102" r:id="rId10"/>
-    <sheet name="2026.06" sheetId="101" r:id="rId11"/>
-    <sheet name="2026.05" sheetId="100" r:id="rId12"/>
-    <sheet name="2026.04" sheetId="99" r:id="rId13"/>
-    <sheet name="2026.03" sheetId="98" r:id="rId14"/>
-    <sheet name="2026.02" sheetId="97" r:id="rId15"/>
-    <sheet name="2026.01" sheetId="69" r:id="rId16"/>
+    <sheet name="2026.08" sheetId="103" r:id="rId10"/>
+    <sheet name="2026.07" sheetId="102" r:id="rId11"/>
+    <sheet name="2026.06" sheetId="101" r:id="rId12"/>
+    <sheet name="2026.05" sheetId="100" r:id="rId13"/>
+    <sheet name="2026.04" sheetId="99" r:id="rId14"/>
+    <sheet name="2026.03" sheetId="98" r:id="rId15"/>
+    <sheet name="2026.02" sheetId="97" r:id="rId16"/>
+    <sheet name="2026.01" sheetId="69" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="48">
   <si>
     <t>Kaina</t>
   </si>
@@ -451,7 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -595,6 +596,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -630,6 +646,24 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -655,24 +689,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -770,7 +786,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40098843-3903-461F-9E13-327F3C68B197}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A6A8BD-52A9-42A5-B9C3-015BF189A509}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -826,7 +842,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDF88B25-9C26-4790-AA0D-F02DB545591A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40098843-3903-461F-9E13-327F3C68B197}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -882,7 +898,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9148C53-3C99-4F68-8D14-4B06E98249CD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDF88B25-9C26-4790-AA0D-F02DB545591A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -938,7 +954,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FB9DC1-5ABE-492E-B51C-1BBC6BCDCACC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9148C53-3C99-4F68-8D14-4B06E98249CD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -994,7 +1010,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{891C8C2D-D9C2-4BB0-A969-9B021DE9AD2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FB9DC1-5ABE-492E-B51C-1BBC6BCDCACC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1050,6 +1066,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{891C8C2D-D9C2-4BB0-A969-9B021DE9AD2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16621125" y="190500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E77520-06CC-410E-98DF-D7780C3359DC}"/>
             </a:ext>
           </a:extLst>
@@ -1085,7 +1157,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1412,31 +1484,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="54" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="59" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="K1" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="58"/>
+      <c r="L1" s="63"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
+      <c r="A2" s="65"/>
       <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
@@ -1462,7 +1534,7 @@
       <c r="I2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="60"/>
+      <c r="J2" s="65"/>
       <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1956,6 +2028,368 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994F0C49-1D2F-4997-8556-A5B08EA369F6}">
+  <dimension ref="A2:X27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="2.7109375" customWidth="1"/>
+    <col min="14" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="24" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q2" s="71">
+        <v>2026.08</v>
+      </c>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q3" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="68" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q5" s="4">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <f>(C19+C29+C39+C49+C59+C69+C79+C89+C99+C109)</f>
+        <v>100</v>
+      </c>
+      <c r="T5" s="4">
+        <f>(I19+I29+I39+I49+I59+I69+I79+I89+I99+I109)-V5</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <f>D19+D29+D39+D49+D59+D69+D79+D89+D99+D109</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <f>J19+J29+J39+J49+J59+J69+J79+J89+J99+J109</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <f>O19+O29+O39+O49+O59+O69+O79+O89+O99+O109</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <f>Q5-S5-U5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="63"/>
+      <c r="P13" s="20"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="82"/>
+      <c r="H14" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="31"/>
+      <c r="N14" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="20"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="41">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>100</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <f>C15/F15</f>
+        <v>12.900000007481999</v>
+      </c>
+      <c r="F15" s="13">
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="G15" s="82"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="44"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="44"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4">
+        <f>SUM(B15:B18)</f>
+        <v>100</v>
+      </c>
+      <c r="C19" s="4">
+        <f>SUM(C15:C18)</f>
+        <v>100</v>
+      </c>
+      <c r="D19" s="4">
+        <f>SUM(D15:D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <f>IF(B19&gt;0,SUMPRODUCT(E15:E18,F15:F18)/SUM(F15:F18),"0.00")</f>
+        <v>12.900000007481999</v>
+      </c>
+      <c r="F19" s="13">
+        <f>SUM(F15:F18)</f>
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="G19" s="83"/>
+      <c r="H19" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="4">
+        <f>SUM(I15:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" ref="J19:L19" si="0">SUM(J15:J18)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="33"/>
+      <c r="N19" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" s="4">
+        <f>SUM(O15:O18)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J27" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q2:X2"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3CE52383-29C5-4497-90B8-DA81B24EC7D1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="E19" formula="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5576365-31FE-4781-A029-EABEF442854F}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1972,54 +2406,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.07</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2054,46 +2488,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2115,7 +2549,7 @@
       <c r="F14" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="50" t="s">
         <v>32</v>
       </c>
@@ -2160,7 +2594,7 @@
       <c r="F15" s="13">
         <v>7.8382191499999996</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2178,7 +2612,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2195,7 +2629,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2212,7 +2646,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2246,7 +2680,7 @@
         <f>SUM(F15:F18)</f>
         <v>7.8382191499999996</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="50" t="s">
         <v>2</v>
       </c>
@@ -2291,6 +2725,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
     <mergeCell ref="Q2:X2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
@@ -2299,11 +2738,6 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{DF2B807C-B133-4C46-9D1B-D6B7BEF50215}"/>
@@ -2317,7 +2751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42AAC754-FACE-4B08-A6F5-27BDC7752425}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2334,54 +2768,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.06</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2416,46 +2850,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2477,7 +2911,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -2522,7 +2956,7 @@
       <c r="F15" s="13">
         <v>8.05542129</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2540,7 +2974,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2557,7 +2991,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2574,7 +3008,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2608,7 +3042,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.05542129</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -2653,11 +3087,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -2666,6 +3095,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{52D9614F-EF79-46CC-8F5E-FBD95649CF20}"/>
@@ -2679,7 +3113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A7359C-5285-4575-BB13-921F668F181E}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2696,54 +3130,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.05</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2778,46 +3212,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2839,7 +3273,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -2884,7 +3318,7 @@
       <c r="F15" s="13">
         <v>8.1859855899999996</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2902,7 +3336,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2919,7 +3353,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2936,7 +3370,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2970,7 +3404,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.1859855899999996</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3015,11 +3449,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3028,6 +3457,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3C02C9E5-EA02-4BDC-91AE-416C94F85838}"/>
@@ -3041,7 +3475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC7392A-0BC5-4BD7-983E-8A7ED64C1BD7}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3058,54 +3492,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.04</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3140,46 +3574,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3201,7 +3635,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3246,7 +3680,7 @@
       <c r="F15" s="13">
         <v>8.6236633299999994</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3264,7 +3698,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3281,7 +3715,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3298,7 +3732,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3332,7 +3766,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.6236633299999994</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3377,11 +3811,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3390,6 +3819,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{5E453430-7CF8-4213-8F80-26238D76E7AB}"/>
@@ -3403,7 +3837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DADF1ABD-D234-4E53-B90E-0B45F09BE5A5}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3420,54 +3854,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.03</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3502,46 +3936,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3563,7 +3997,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3608,7 +4042,7 @@
       <c r="F15" s="13">
         <v>9.0073860499999991</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3626,7 +4060,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3643,7 +4077,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3660,7 +4094,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3694,7 +4128,7 @@
         <f>SUM(F15:F18)</f>
         <v>9.0073860499999991</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3739,11 +4173,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3752,6 +4181,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{04427A72-C2D7-400B-ACC4-6F6AA44B6641}"/>
@@ -3765,7 +4199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3782,54 +4216,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.02</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3864,46 +4298,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3925,7 +4359,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3970,7 +4404,7 @@
       <c r="F15" s="13">
         <v>8.7032201899999997</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3988,7 +4422,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4005,7 +4439,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4022,7 +4456,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4056,7 +4490,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7032201899999997</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4101,11 +4535,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -4114,6 +4543,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{BF7DD392-2323-41A9-A80E-2E9F0505699A}"/>
@@ -4127,7 +4561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4144,54 +4578,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="75">
+      <c r="Q2" s="71">
         <v>2026.01</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="78" t="s">
+      <c r="Q3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="78" t="s">
+      <c r="R3" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="78" t="s">
+      <c r="T3" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="63" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="63" t="s">
+      <c r="X3" s="68" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -4226,46 +4660,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="69"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="80"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="58"/>
+      <c r="O13" s="63"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -4287,7 +4721,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4332,7 +4766,7 @@
       <c r="F15" s="13">
         <v>8.7351502399999994</v>
       </c>
-      <c r="G15" s="71"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4350,7 +4784,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="71"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4367,7 +4801,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="71"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4384,7 +4818,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="71"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4418,7 +4852,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7351502399999994</v>
       </c>
-      <c r="G19" s="72"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4513,59 +4947,59 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
-      <c r="W3" s="59" t="s">
+      <c r="V3" s="63"/>
+      <c r="W3" s="64" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -4599,20 +5033,20 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="60"/>
+      <c r="W4" s="65"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -5334,59 +5768,59 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
-      <c r="W3" s="59" t="s">
+      <c r="V3" s="63"/>
+      <c r="W3" s="64" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -5420,20 +5854,20 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="60"/>
+      <c r="W4" s="65"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="e">
@@ -5943,56 +6377,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
+      <c r="V3" s="63"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6026,13 +6460,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -6437,56 +6871,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
+      <c r="V3" s="63"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6520,13 +6954,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -6832,12 +7266,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -6845,6 +7273,12 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6878,56 +7312,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
+      <c r="V3" s="63"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6961,13 +7395,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -7273,12 +7707,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -7286,6 +7714,12 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7319,56 +7753,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
+      <c r="V3" s="63"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -7402,13 +7836,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -7707,56 +8141,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="58"/>
+      <c r="V3" s="63"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -7790,13 +8224,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -8049,11 +8483,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="K3:L3"/>
@@ -8062,6 +8491,11 @@
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8095,74 +8529,74 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="62" t="s">
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="67"/>
+      <c r="M3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="63" t="s">
+      <c r="S3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="57" t="s">
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
+      <c r="V3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="58"/>
-      <c r="X3" s="59" t="s">
+      <c r="W3" s="63"/>
+      <c r="X3" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" s="59" t="s">
+      <c r="Y3" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" s="63" t="s">
+      <c r="AC3" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="AD3" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="63" t="s">
+      <c r="AD3" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AF3" s="64" t="s">
+      <c r="AF3" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="65"/>
+      <c r="AG3" s="70"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -8196,11 +8630,11 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
+      <c r="M4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
       <c r="S4" s="38" t="s">
         <v>45</v>
       </c>
@@ -8216,11 +8650,11 @@
       <c r="W4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="AC4" s="68"/>
+      <c r="AD4" s="68"/>
+      <c r="AE4" s="68"/>
       <c r="AF4" s="45" t="s">
         <v>32</v>
       </c>
@@ -8285,18 +8719,18 @@
       </c>
       <c r="P5" s="4">
         <f>SUM(B5:B200)</f>
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Q5" s="13">
         <f>SUM(E5:E200)</f>
-        <v>59.149045839999999</v>
+        <v>66.900983819999993</v>
       </c>
       <c r="R5" s="4">
         <v>0</v>
       </c>
       <c r="S5" s="4">
         <f>R5-P5+X5</f>
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="T5" s="21">
         <f>(R5-P5+X5)/P5</f>
@@ -8304,7 +8738,7 @@
       </c>
       <c r="U5" s="21">
         <f ca="1">XIRR(AG5:AG40,AF5:AF40)</f>
-        <v>0.23612903952598571</v>
+        <v>0.23278971314430238</v>
       </c>
       <c r="V5" s="4">
         <f>SUM(K5:K200)</f>
@@ -8320,7 +8754,7 @@
       </c>
       <c r="Y5" s="4" cm="1">
         <f t="array" ref="Y5">SUMPRODUCT(IFERROR(AD5:AD200,0),IFERROR(AE5:AE200,0))/SUM(IFERROR(AE5:AE200,0))</f>
-        <v>11.834510431385853</v>
+        <v>11.942568488494429</v>
       </c>
       <c r="AC5" s="4">
         <f>'2026.01'!$C$19</f>
@@ -8782,24 +9216,77 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="4"/>
+      <c r="A12" s="36">
+        <f>'2026.08'!$Q$2</f>
+        <v>2026.08</v>
+      </c>
+      <c r="B12" s="4">
+        <f>'2026.08'!$B$15</f>
+        <v>100</v>
+      </c>
+      <c r="C12" s="4">
+        <f>'2026.08'!$C$15</f>
+        <v>100</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" ref="D12" si="8">C12+D11</f>
+        <v>800</v>
+      </c>
+      <c r="E12" s="13">
+        <f>'2026.08'!$F$15</f>
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="F12" s="13">
+        <f t="shared" ref="F12" si="9">E12+F11</f>
+        <v>66.900983819999993</v>
+      </c>
+      <c r="G12" s="53">
+        <v>12.86</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" ref="H12" si="10">F12*G12</f>
+        <v>860.34665192519992</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" ref="I12" si="11">H12-D12</f>
+        <v>60.346651925199922</v>
+      </c>
+      <c r="J12" s="21">
+        <f t="shared" ref="J12" si="12">(H12-D12)/D12</f>
+        <v>7.5433314906499904E-2</v>
+      </c>
+      <c r="K12" s="4">
+        <f>'2026.08'!$D$15</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <f>'2026.08'!$J$15</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <f>'2026.08'!$O$15</f>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4">
+        <f>'2026.07'!$C$19</f>
+        <v>100</v>
+      </c>
+      <c r="AD12" s="4">
+        <f>'2026.07'!$E$19</f>
+        <v>12.758000010754994</v>
+      </c>
+      <c r="AE12" s="5">
+        <f>'2026.07'!$F$19</f>
+        <v>7.8382191499999996</v>
+      </c>
+      <c r="AF12" s="47">
+        <f>'2026.07'!$A$15</f>
+        <v>46218</v>
+      </c>
+      <c r="AG12" s="4">
+        <f>'2026.07'!$B$15*-1</f>
+        <v>-100</v>
+      </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
@@ -9085,33 +9572,33 @@
       <c r="AE36" s="5"/>
       <c r="AF36" s="47">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="AG36" s="4" cm="1">
         <f t="array" ref="AG36">LOOKUP(2,1/(H:H&gt;0),H:H)</f>
-        <v>744.80478521728003</v>
+        <v>860.34665192519992</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:U3"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="Y3:Y4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" location="'2026.01'!A1" display="'2026.01'!A1" xr:uid="{BAF6215B-37D5-4AB2-9B9C-F1057A1F97E5}"/>
@@ -9121,11 +9608,12 @@
     <hyperlink ref="A9" location="'2026.05'!A1" display="'2026.05'!A1" xr:uid="{E2054D31-1D52-46BB-B8EA-FBB4811DE31D}"/>
     <hyperlink ref="A10" location="'2026.06'!A1" display="'2026.06'!A1" xr:uid="{F3608F29-46AC-4471-94DD-E0C306FF3FA3}"/>
     <hyperlink ref="A11" location="'2026.07'!A1" display="'2026.07'!A1" xr:uid="{D0DD87A1-01F2-4AC6-948E-9098F2EEF6C1}"/>
+    <hyperlink ref="A12" location="'2026.08'!A1" display="'2026.08'!A1" xr:uid="{08493110-847F-414B-BF99-AD3F9DD09E97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="E5:E11" formula="1"/>
+    <ignoredError sqref="E5:E12" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/excel/Revolut Brokerage Rima.xlsx
+++ b/excel/Revolut Brokerage Rima.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Revolut\Brokerage Account Rima\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69be8bcaca992739/Dokumentai/portfolio-analytics/portfolio-dashboard-clean/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EE1FC9-214D-466E-AEDD-AC0AB94F2565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C1EE1FC9-214D-466E-AEDD-AC0AB94F2565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423C2149-F0E0-425C-A1BC-50329235457A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="81" r:id="rId1"/>
@@ -646,24 +646,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -689,6 +671,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1893,18 +1893,54 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="36">
+        <f>'2026.08'!$Q$2</f>
+        <v>2026.08</v>
+      </c>
+      <c r="B10" s="4">
+        <f>B9+'2026.08'!$Q$5</f>
+        <v>800</v>
+      </c>
+      <c r="C10" s="4">
+        <f>'2026.08'!$R$5</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <f>D9+'2026.08'!$S$5-K10-L10</f>
+        <v>800</v>
+      </c>
+      <c r="E10" s="4">
+        <f>'2026.08'!$X$5</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <f>WEBN!H12</f>
+        <v>860.34665192519992</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" ref="G10" si="6">SUM(F10:F10)+E10</f>
+        <v>860.34665192519992</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" ref="H10" si="7">G10-B10</f>
+        <v>60.346651925199922</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" ref="I10" si="8">H10/B10</f>
+        <v>7.5433314906499904E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <f>'2026.08'!$W$5</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <f>'2026.08'!$U$5</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <f>'2026.08'!$V$5</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -2021,6 +2057,7 @@
     <hyperlink ref="F2" location="WEBN!A1" display="WEBN!A1" xr:uid="{499756ED-B1F9-4D05-897B-F69DF5557EF9}"/>
     <hyperlink ref="A8" location="'2026.06'!A1" display="'2026.06'!A1" xr:uid="{EDD493B5-6E5A-4B6F-9C2F-600CF21AFF32}"/>
     <hyperlink ref="A9" location="'2026.07'!A1" display="'2026.07'!A1" xr:uid="{0EA64D34-DE59-4B69-AFFB-31BBE94C6E84}"/>
+    <hyperlink ref="A10" location="'2026.08'!A1" display="'2026.08'!A1" xr:uid="{EBA7FF03-B603-4FA0-A3D1-936DE1CCCC75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2044,34 +2081,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.08</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -2126,23 +2163,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -2153,14 +2190,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -2187,7 +2224,7 @@
       <c r="F14" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="56" t="s">
         <v>32</v>
       </c>
@@ -2232,7 +2269,7 @@
       <c r="F15" s="13">
         <v>7.7519379800000001</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2250,7 +2287,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2267,7 +2304,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2284,7 +2321,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2318,7 +2355,7 @@
         <f>SUM(F15:F18)</f>
         <v>7.7519379800000001</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="56" t="s">
         <v>2</v>
       </c>
@@ -2363,11 +2400,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
     <mergeCell ref="Q2:X2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
@@ -2376,6 +2408,11 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3CE52383-29C5-4497-90B8-DA81B24EC7D1}"/>
@@ -2406,34 +2443,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.07</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -2488,23 +2525,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -2515,14 +2552,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -2549,7 +2586,7 @@
       <c r="F14" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="50" t="s">
         <v>32</v>
       </c>
@@ -2594,7 +2631,7 @@
       <c r="F15" s="13">
         <v>7.8382191499999996</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2612,7 +2649,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2629,7 +2666,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2646,7 +2683,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2680,7 +2717,7 @@
         <f>SUM(F15:F18)</f>
         <v>7.8382191499999996</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="50" t="s">
         <v>2</v>
       </c>
@@ -2725,11 +2762,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
     <mergeCell ref="Q2:X2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
@@ -2738,6 +2770,11 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{DF2B807C-B133-4C46-9D1B-D6B7BEF50215}"/>
@@ -2768,34 +2805,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.06</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -2850,23 +2887,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -2877,14 +2914,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -2911,7 +2948,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -2956,7 +2993,7 @@
       <c r="F15" s="13">
         <v>8.05542129</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -2974,7 +3011,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2991,7 +3028,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3008,7 +3045,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3042,7 +3079,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.05542129</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3087,6 +3124,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3095,11 +3137,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{52D9614F-EF79-46CC-8F5E-FBD95649CF20}"/>
@@ -3130,34 +3167,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.05</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -3212,23 +3249,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -3239,14 +3276,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -3273,7 +3310,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3318,7 +3355,7 @@
       <c r="F15" s="13">
         <v>8.1859855899999996</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3336,7 +3373,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3353,7 +3390,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3370,7 +3407,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3404,7 +3441,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.1859855899999996</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3449,6 +3486,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3457,11 +3499,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3C02C9E5-EA02-4BDC-91AE-416C94F85838}"/>
@@ -3492,34 +3529,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.04</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -3574,23 +3611,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -3601,14 +3638,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -3635,7 +3672,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3680,7 +3717,7 @@
       <c r="F15" s="13">
         <v>8.6236633299999994</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3698,7 +3735,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3715,7 +3752,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3732,7 +3769,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3766,7 +3803,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.6236633299999994</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3811,6 +3848,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3819,11 +3861,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{5E453430-7CF8-4213-8F80-26238D76E7AB}"/>
@@ -3854,34 +3891,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.03</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -3936,23 +3973,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -3963,14 +4000,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -3997,7 +4034,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4042,7 +4079,7 @@
       <c r="F15" s="13">
         <v>9.0073860499999991</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4060,7 +4097,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4077,7 +4114,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4094,7 +4131,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4128,7 +4165,7 @@
         <f>SUM(F15:F18)</f>
         <v>9.0073860499999991</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4173,6 +4210,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -4181,11 +4223,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{04427A72-C2D7-400B-ACC4-6F6AA44B6641}"/>
@@ -4216,34 +4253,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.02</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -4298,23 +4335,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -4325,14 +4362,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -4359,7 +4396,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4404,7 +4441,7 @@
       <c r="F15" s="13">
         <v>8.7032201899999997</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4422,7 +4459,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4439,7 +4476,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4456,7 +4493,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4490,7 +4527,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7032201899999997</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4535,6 +4572,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -4543,11 +4585,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{BF7DD392-2323-41A9-A80E-2E9F0505699A}"/>
@@ -4578,34 +4615,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="71">
+      <c r="Q2" s="80">
         <v>2026.01</v>
       </c>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="73"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="74" t="s">
+      <c r="Q3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="74" t="s">
+      <c r="T3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="75" t="s">
+      <c r="U3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="76"/>
+      <c r="V3" s="85"/>
       <c r="W3" s="68" t="s">
         <v>39</v>
       </c>
@@ -4660,23 +4697,23 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="80"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
@@ -4687,14 +4724,14 @@
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="84" t="s">
+      <c r="G13" s="75"/>
+      <c r="H13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
       <c r="M13" s="30"/>
       <c r="N13" s="62" t="s">
         <v>39</v>
@@ -4721,7 +4758,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="82"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4766,7 +4803,7 @@
       <c r="F15" s="13">
         <v>8.7351502399999994</v>
       </c>
-      <c r="G15" s="82"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4784,7 +4821,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4801,7 +4838,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4818,7 +4855,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4852,7 +4889,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7351502399999994</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -7266,6 +7303,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -7273,12 +7316,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7707,6 +7744,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -7714,12 +7757,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8483,6 +8520,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="K3:L3"/>
@@ -8491,11 +8533,6 @@
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9581,24 +9618,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="AC3:AC4"/>
     <mergeCell ref="AD3:AD4"/>
     <mergeCell ref="AE3:AE4"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:U3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" location="'2026.01'!A1" display="'2026.01'!A1" xr:uid="{BAF6215B-37D5-4AB2-9B9C-F1057A1F97E5}"/>
